--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/76.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/76.xlsx
@@ -426,13 +426,13 @@
         <v>-6.746239582533168</v>
       </c>
       <c r="E2">
-        <v>-7.124965458834654</v>
+        <v>-13.21218193523948</v>
       </c>
       <c r="F2">
-        <v>-1.98728253942262</v>
+        <v>-2.301994226359402</v>
       </c>
       <c r="G2">
-        <v>-10.06583226739643</v>
+        <v>-12.14474207785402</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-6.424277080689084</v>
       </c>
       <c r="E3">
-        <v>-8.170789755751054</v>
+        <v>-14.2327837797802</v>
       </c>
       <c r="F3">
-        <v>-1.806607325198019</v>
+        <v>-2.387556295394563</v>
       </c>
       <c r="G3">
-        <v>-9.725139235862212</v>
+        <v>-11.00505285553861</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-6.042977598541276</v>
       </c>
       <c r="E4">
-        <v>-9.213939384574264</v>
+        <v>-14.16163096336323</v>
       </c>
       <c r="F4">
-        <v>-1.965979414924825</v>
+        <v>-2.527767418727213</v>
       </c>
       <c r="G4">
-        <v>-9.387447255235481</v>
+        <v>-10.89510787394535</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-5.628148986535498</v>
       </c>
       <c r="E5">
-        <v>-7.646039811281618</v>
+        <v>-14.53667009920657</v>
       </c>
       <c r="F5">
-        <v>-1.289417793994954</v>
+        <v>-2.317729893542982</v>
       </c>
       <c r="G5">
-        <v>-9.642571827423662</v>
+        <v>-10.64031617169254</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-5.176211464447472</v>
       </c>
       <c r="E6">
-        <v>-9.741729479733475</v>
+        <v>-15.15467209755239</v>
       </c>
       <c r="F6">
-        <v>-1.060144749350315</v>
+        <v>-2.336648148288117</v>
       </c>
       <c r="G6">
-        <v>-9.109153630173465</v>
+        <v>-10.05806399686557</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-4.689183734143161</v>
       </c>
       <c r="E7">
-        <v>-9.996703429387349</v>
+        <v>-16.01463188126006</v>
       </c>
       <c r="F7">
-        <v>-1.695852118341517</v>
+        <v>-2.476865070192587</v>
       </c>
       <c r="G7">
-        <v>-8.513833373295675</v>
+        <v>-9.925496913390313</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-4.154588004300536</v>
       </c>
       <c r="E8">
-        <v>-11.25426259285483</v>
+        <v>-16.64121856741429</v>
       </c>
       <c r="F8">
-        <v>-1.497107725959651</v>
+        <v>-2.365255816543798</v>
       </c>
       <c r="G8">
-        <v>-8.208684323997172</v>
+        <v>-9.801670602806107</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-3.567087572196422</v>
       </c>
       <c r="E9">
-        <v>-11.55554900199187</v>
+        <v>-17.12613090885597</v>
       </c>
       <c r="F9">
-        <v>-1.60073068947805</v>
+        <v>-2.199790256201999</v>
       </c>
       <c r="G9">
-        <v>-8.126060784549916</v>
+        <v>-8.817241055951905</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-2.912601141447911</v>
       </c>
       <c r="E10">
-        <v>-12.37752351492266</v>
+        <v>-17.25160772940169</v>
       </c>
       <c r="F10">
-        <v>-1.492522712385156</v>
+        <v>-2.052677175669224</v>
       </c>
       <c r="G10">
-        <v>-7.974842541715747</v>
+        <v>-8.558088104859637</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-2.193811731466825</v>
       </c>
       <c r="E11">
-        <v>-13.5822330642817</v>
+        <v>-17.86756634777569</v>
       </c>
       <c r="F11">
-        <v>-1.066268869559212</v>
+        <v>-2.012501356633448</v>
       </c>
       <c r="G11">
-        <v>-6.859510261063127</v>
+        <v>-8.057625336583062</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-1.429617522508685</v>
       </c>
       <c r="E12">
-        <v>-13.18972136839481</v>
+        <v>-18.48241605872596</v>
       </c>
       <c r="F12">
-        <v>-0.9267527464775106</v>
+        <v>-1.893324966760086</v>
       </c>
       <c r="G12">
-        <v>-6.496418346309455</v>
+        <v>-7.765637050768362</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-0.649544085845713</v>
       </c>
       <c r="E13">
-        <v>-14.47866634984402</v>
+        <v>-19.43652498995617</v>
       </c>
       <c r="F13">
-        <v>-1.179838868850427</v>
+        <v>-1.741269017934806</v>
       </c>
       <c r="G13">
-        <v>-6.221582652458369</v>
+        <v>-7.212621299244972</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>0.09777623971313766</v>
       </c>
       <c r="E14">
-        <v>-15.48140938568797</v>
+        <v>-19.7803652023274</v>
       </c>
       <c r="F14">
-        <v>-0.9602063640395687</v>
+        <v>-1.676465007646398</v>
       </c>
       <c r="G14">
-        <v>-5.647294554006588</v>
+        <v>-6.477947328327329</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>0.7696218870390622</v>
       </c>
       <c r="E15">
-        <v>-15.06988844156734</v>
+        <v>-20.90397499414651</v>
       </c>
       <c r="F15">
-        <v>-0.4197935526990188</v>
+        <v>-1.788505840712045</v>
       </c>
       <c r="G15">
-        <v>-5.431213667178506</v>
+        <v>-5.674631660620135</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>1.333439308078166</v>
       </c>
       <c r="E16">
-        <v>-16.80724734333564</v>
+        <v>-21.28132331548646</v>
       </c>
       <c r="F16">
-        <v>-0.1049874318783171</v>
+        <v>-1.05854848536512</v>
       </c>
       <c r="G16">
-        <v>-4.36740051491462</v>
+        <v>-6.158102397725449</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>1.768371970618348</v>
       </c>
       <c r="E17">
-        <v>-18.06530904537343</v>
+        <v>-21.82350013467488</v>
       </c>
       <c r="F17">
-        <v>0.02372263843386449</v>
+        <v>-1.089372864790693</v>
       </c>
       <c r="G17">
-        <v>-4.662628734766892</v>
+        <v>-5.336644665854609</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>2.078876378502037</v>
       </c>
       <c r="E18">
-        <v>-17.47255857188257</v>
+        <v>-22.35617440635209</v>
       </c>
       <c r="F18">
-        <v>-0.06817561286530986</v>
+        <v>-0.871759091340457</v>
       </c>
       <c r="G18">
-        <v>-4.479187376816909</v>
+        <v>-5.804876486781595</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>2.280342066373285</v>
       </c>
       <c r="E19">
-        <v>-18.82012197797042</v>
+        <v>-23.00261759585032</v>
       </c>
       <c r="F19">
-        <v>0.7770822012772777</v>
+        <v>-0.4876078501292003</v>
       </c>
       <c r="G19">
-        <v>-2.923765796557209</v>
+        <v>-5.264812639174719</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>2.399689000299942</v>
       </c>
       <c r="E20">
-        <v>-20.20112288843445</v>
+        <v>-23.95303847542409</v>
       </c>
       <c r="F20">
-        <v>0.7032357324199101</v>
+        <v>-0.1784876431613144</v>
       </c>
       <c r="G20">
-        <v>-3.481530492491833</v>
+        <v>-5.35821985915557</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>2.471281380082146</v>
       </c>
       <c r="E21">
-        <v>-19.69903701816461</v>
+        <v>-24.86311921339979</v>
       </c>
       <c r="F21">
-        <v>0.8011313637153529</v>
+        <v>0.1417972996615032</v>
       </c>
       <c r="G21">
-        <v>-3.375335845503709</v>
+        <v>-5.061273769362344</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>2.52140830892735</v>
       </c>
       <c r="E22">
-        <v>-20.78656370999361</v>
+        <v>-24.77600975907283</v>
       </c>
       <c r="F22">
-        <v>0.7848489740459258</v>
+        <v>0.2097317103650907</v>
       </c>
       <c r="G22">
-        <v>-3.005907653627406</v>
+        <v>-5.443471113033783</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>2.575895396949987</v>
       </c>
       <c r="E23">
-        <v>-21.05370241561791</v>
+        <v>-25.52122462029815</v>
       </c>
       <c r="F23">
-        <v>0.7280826126668813</v>
+        <v>0.3432637073289682</v>
       </c>
       <c r="G23">
-        <v>-2.9462129785516</v>
+        <v>-5.03331008404693</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>2.651116564195149</v>
       </c>
       <c r="E24">
-        <v>-20.46900917209722</v>
+        <v>-25.24567566174107</v>
       </c>
       <c r="F24">
-        <v>1.379691322322223</v>
+        <v>0.511880377271016</v>
       </c>
       <c r="G24">
-        <v>-2.369191430512924</v>
+        <v>-4.659989271985276</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>2.755277499810458</v>
       </c>
       <c r="E25">
-        <v>-21.94523491181693</v>
+        <v>-25.92939392287964</v>
       </c>
       <c r="F25">
-        <v>1.386300037461757</v>
+        <v>0.4804786257656923</v>
       </c>
       <c r="G25">
-        <v>-3.229413498072614</v>
+        <v>-5.463850585312013</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>2.895367589146179</v>
       </c>
       <c r="E26">
-        <v>-20.59498853121324</v>
+        <v>-26.07160818506442</v>
       </c>
       <c r="F26">
-        <v>1.764436502961287</v>
+        <v>0.8102019867760075</v>
       </c>
       <c r="G26">
-        <v>-2.954739670386176</v>
+        <v>-5.030229405429417</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>3.069810972240115</v>
       </c>
       <c r="E27">
-        <v>-21.65178561244984</v>
+        <v>-26.96727312653165</v>
       </c>
       <c r="F27">
-        <v>1.55189399475099</v>
+        <v>0.902533474226846</v>
       </c>
       <c r="G27">
-        <v>-3.469129455684045</v>
+        <v>-5.583696815767069</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>3.275922221370152</v>
       </c>
       <c r="E28">
-        <v>-20.79983737338776</v>
+        <v>-26.16462765910661</v>
       </c>
       <c r="F28">
-        <v>1.728468790331732</v>
+        <v>0.7352065723309571</v>
       </c>
       <c r="G28">
-        <v>-3.033722526501127</v>
+        <v>-5.302561395217626</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>3.505852017903686</v>
       </c>
       <c r="E29">
-        <v>-19.43615950735958</v>
+        <v>-26.03502669971533</v>
       </c>
       <c r="F29">
-        <v>1.496739636337793</v>
+        <v>0.4871660358084927</v>
       </c>
       <c r="G29">
-        <v>-3.819869937777159</v>
+        <v>-5.607778323875498</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>3.747165726489605</v>
       </c>
       <c r="E30">
-        <v>-20.58573932959285</v>
+        <v>-25.96396110073619</v>
       </c>
       <c r="F30">
-        <v>1.574738710985394</v>
+        <v>0.7579833624383323</v>
       </c>
       <c r="G30">
-        <v>-3.831547798333209</v>
+        <v>-5.95110429132985</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>3.988698156591136</v>
       </c>
       <c r="E31">
-        <v>-20.89277378320345</v>
+        <v>-25.91047189208373</v>
       </c>
       <c r="F31">
-        <v>1.611466864890719</v>
+        <v>0.9048562164242958</v>
       </c>
       <c r="G31">
-        <v>-3.173616664671341</v>
+        <v>-4.987770866144141</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>4.215829305735681</v>
       </c>
       <c r="E32">
-        <v>-21.41989521133936</v>
+        <v>-24.52545482626858</v>
       </c>
       <c r="F32">
-        <v>1.51526193146439</v>
+        <v>0.6599013484772596</v>
       </c>
       <c r="G32">
-        <v>-3.766213914940599</v>
+        <v>-5.711390944463011</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>4.416074092815262</v>
       </c>
       <c r="E33">
-        <v>-20.22396555072101</v>
+        <v>-24.94350461859185</v>
       </c>
       <c r="F33">
-        <v>1.653637392632436</v>
+        <v>0.6561886057779123</v>
       </c>
       <c r="G33">
-        <v>-3.96651023997081</v>
+        <v>-5.841218051489892</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>4.581746329180185</v>
       </c>
       <c r="E34">
-        <v>-19.51552737577705</v>
+        <v>-25.1195883191306</v>
       </c>
       <c r="F34">
-        <v>1.382111811873203</v>
+        <v>0.7588680588245221</v>
       </c>
       <c r="G34">
-        <v>-3.654314791020893</v>
+        <v>-5.550717890092125</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>4.706286705231823</v>
       </c>
       <c r="E35">
-        <v>-18.4299319272141</v>
+        <v>-24.16881856980555</v>
       </c>
       <c r="F35">
-        <v>1.590245748765801</v>
+        <v>0.8828067328965785</v>
       </c>
       <c r="G35">
-        <v>-3.197551971082667</v>
+        <v>-5.78821471480111</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>4.790197262220293</v>
       </c>
       <c r="E36">
-        <v>-19.04716142825349</v>
+        <v>-23.21658689009416</v>
       </c>
       <c r="F36">
-        <v>1.419270716827983</v>
+        <v>0.8703994459374476</v>
       </c>
       <c r="G36">
-        <v>-3.353186288392704</v>
+        <v>-5.98342008787865</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>4.835977126457335</v>
       </c>
       <c r="E37">
-        <v>-17.62111478776036</v>
+        <v>-23.19660163719909</v>
       </c>
       <c r="F37">
-        <v>1.625739635240954</v>
+        <v>0.7856574606310581</v>
       </c>
       <c r="G37">
-        <v>-3.233917032492284</v>
+        <v>-5.556135185118685</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>4.849576470934865</v>
       </c>
       <c r="E38">
-        <v>-17.910223981293</v>
+        <v>-22.6743187002566</v>
       </c>
       <c r="F38">
-        <v>1.222780312149135</v>
+        <v>0.6775406039524723</v>
       </c>
       <c r="G38">
-        <v>-4.472415105347561</v>
+        <v>-5.566288370833525</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>4.843513649849106</v>
       </c>
       <c r="E39">
-        <v>-16.13794487870554</v>
+        <v>-21.97826540148329</v>
       </c>
       <c r="F39">
-        <v>1.501782737086036</v>
+        <v>0.8060071342482308</v>
       </c>
       <c r="G39">
-        <v>-3.965732238082659</v>
+        <v>-5.636496514377743</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>4.828070697062274</v>
       </c>
       <c r="E40">
-        <v>-16.72959475119532</v>
+        <v>-21.33882452627871</v>
       </c>
       <c r="F40">
-        <v>1.597462485578991</v>
+        <v>0.8582555798124069</v>
       </c>
       <c r="G40">
-        <v>-3.934625216279544</v>
+        <v>-5.690920096124091</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>4.813572578145036</v>
       </c>
       <c r="E41">
-        <v>-15.53533468152955</v>
+        <v>-21.56709332711393</v>
       </c>
       <c r="F41">
-        <v>1.540717661752419</v>
+        <v>0.8708948096443216</v>
       </c>
       <c r="G41">
-        <v>-3.919169608300153</v>
+        <v>-5.937711171577439</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>4.808434068947959</v>
       </c>
       <c r="E42">
-        <v>-16.71405758762914</v>
+        <v>-20.83852453687854</v>
       </c>
       <c r="F42">
-        <v>1.119298999456615</v>
+        <v>0.7699549281435907</v>
       </c>
       <c r="G42">
-        <v>-3.705232142781375</v>
+        <v>-5.752063734447964</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>4.815598001265855</v>
       </c>
       <c r="E43">
-        <v>-14.94530456145645</v>
+        <v>-19.33532368960407</v>
       </c>
       <c r="F43">
-        <v>1.111984515289896</v>
+        <v>0.7184387593634894</v>
       </c>
       <c r="G43">
-        <v>-3.914180475386535</v>
+        <v>-5.787353169086042</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>4.836709306407937</v>
       </c>
       <c r="E44">
-        <v>-13.78064442890274</v>
+        <v>-18.90830296081917</v>
       </c>
       <c r="F44">
-        <v>0.9249789173731015</v>
+        <v>0.6363425795416416</v>
       </c>
       <c r="G44">
-        <v>-3.753115809326984</v>
+        <v>-5.887872057333086</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>4.865935831350844</v>
       </c>
       <c r="E45">
-        <v>-12.91842945144568</v>
+        <v>-19.0573990941692</v>
       </c>
       <c r="F45">
-        <v>1.338917422021626</v>
+        <v>0.5954874992355701</v>
       </c>
       <c r="G45">
-        <v>-4.313801928459064</v>
+        <v>-5.46602533555641</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>4.896569813905577</v>
       </c>
       <c r="E46">
-        <v>-12.67054503352329</v>
+        <v>-18.8840025213576</v>
       </c>
       <c r="F46">
-        <v>1.142741796955841</v>
+        <v>0.7477811895054536</v>
       </c>
       <c r="G46">
-        <v>-3.176446711808108</v>
+        <v>-5.53243745646515</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>4.919917325370741</v>
       </c>
       <c r="E47">
-        <v>-12.68541353006618</v>
+        <v>-17.35960368348121</v>
       </c>
       <c r="F47">
-        <v>0.638435863968516</v>
+        <v>0.6227010251523394</v>
       </c>
       <c r="G47">
-        <v>-3.820979504228383</v>
+        <v>-6.172002001928536</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>4.922241489300034</v>
       </c>
       <c r="E48">
-        <v>-12.30014918794111</v>
+        <v>-17.84591565713936</v>
       </c>
       <c r="F48">
-        <v>1.305724740191449</v>
+        <v>0.6803587098567963</v>
       </c>
       <c r="G48">
-        <v>-4.29331802639719</v>
+        <v>-6.436076206575054</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>4.891786266875799</v>
       </c>
       <c r="E49">
-        <v>-11.99588907949549</v>
+        <v>-16.62343451652137</v>
       </c>
       <c r="F49">
-        <v>1.073347802888521</v>
+        <v>0.6564230337529045</v>
       </c>
       <c r="G49">
-        <v>-4.47782978962953</v>
+        <v>-6.163864311038036</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>4.814725211715196</v>
       </c>
       <c r="E50">
-        <v>-11.08263944127894</v>
+        <v>-16.16982908204625</v>
       </c>
       <c r="F50">
-        <v>0.699497310331076</v>
+        <v>0.4870641466179483</v>
       </c>
       <c r="G50">
-        <v>-4.260401758592433</v>
+        <v>-5.976598212262071</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>4.68195456810946</v>
       </c>
       <c r="E51">
-        <v>-10.67358965789658</v>
+        <v>-15.76119046658505</v>
       </c>
       <c r="F51">
-        <v>0.8376209478086711</v>
+        <v>0.2371539848673655</v>
       </c>
       <c r="G51">
-        <v>-3.904617317949288</v>
+        <v>-6.306316978907542</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>4.488460925708641</v>
       </c>
       <c r="E52">
-        <v>-9.904759637078296</v>
+        <v>-15.49019758085131</v>
       </c>
       <c r="F52">
-        <v>0.7703956196018801</v>
+        <v>0.5093339758748102</v>
       </c>
       <c r="G52">
-        <v>-4.388931325557531</v>
+        <v>-6.019939183219143</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>4.22873590211965</v>
       </c>
       <c r="E53">
-        <v>-10.19944244020886</v>
+        <v>-15.44174621753586</v>
       </c>
       <c r="F53">
-        <v>1.126177762369462</v>
+        <v>0.1457618660513016</v>
       </c>
       <c r="G53">
-        <v>-4.184823313424294</v>
+        <v>-6.536407121211537</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>3.905126067822673</v>
       </c>
       <c r="E54">
-        <v>-9.831243643417505</v>
+        <v>-14.61951005229161</v>
       </c>
       <c r="F54">
-        <v>0.9430886855331042</v>
+        <v>0.3307876658754048</v>
       </c>
       <c r="G54">
-        <v>-4.486573173265168</v>
+        <v>-6.631359901990328</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>3.517417960222847</v>
       </c>
       <c r="E55">
-        <v>-9.880180932457961</v>
+        <v>-14.75335559365685</v>
       </c>
       <c r="F55">
-        <v>0.7767160628852403</v>
+        <v>0.3926981888258343</v>
       </c>
       <c r="G55">
-        <v>-4.952042826414756</v>
+        <v>-6.33321286968519</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>3.068127724410953</v>
       </c>
       <c r="E56">
-        <v>-8.92495478738137</v>
+        <v>-14.0067120277358</v>
       </c>
       <c r="F56">
-        <v>0.4127537920150131</v>
+        <v>-0.007020560986233562</v>
       </c>
       <c r="G56">
-        <v>-4.542116764441103</v>
+        <v>-6.811013069538606</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>2.565643945728455</v>
       </c>
       <c r="E57">
-        <v>-8.602798491337069</v>
+        <v>-14.0080992003183</v>
       </c>
       <c r="F57">
-        <v>0.8242477844578759</v>
+        <v>0.3938827542118375</v>
       </c>
       <c r="G57">
-        <v>-5.469171282788702</v>
+        <v>-6.735382409478645</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>2.013729039471546</v>
       </c>
       <c r="E58">
-        <v>-8.107220703213228</v>
+        <v>-13.12938766747902</v>
       </c>
       <c r="F58">
-        <v>0.5055524786810305</v>
+        <v>0.3280855314074728</v>
       </c>
       <c r="G58">
-        <v>-5.935763556112469</v>
+        <v>-7.61435223394712</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>1.423082979445759</v>
       </c>
       <c r="E59">
-        <v>-7.267848388042731</v>
+        <v>-13.52902627399932</v>
       </c>
       <c r="F59">
-        <v>0.3017848663685885</v>
+        <v>0.3885737475272956</v>
       </c>
       <c r="G59">
-        <v>-5.509039963439593</v>
+        <v>-7.10896429599941</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>0.8026026769711617</v>
       </c>
       <c r="E60">
-        <v>-8.16982205751237</v>
+        <v>-13.43488958611076</v>
       </c>
       <c r="F60">
-        <v>0.225302532435513</v>
+        <v>0.1285376226448915</v>
       </c>
       <c r="G60">
-        <v>-5.775938993733695</v>
+        <v>-7.365576992604526</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>0.1591587057528237</v>
       </c>
       <c r="E61">
-        <v>-7.830388402356783</v>
+        <v>-12.19764793244434</v>
       </c>
       <c r="F61">
-        <v>0.4559125620682701</v>
+        <v>0.094573730762709</v>
       </c>
       <c r="G61">
-        <v>-6.397807912358515</v>
+        <v>-7.822675293222709</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-0.4919001125646809</v>
       </c>
       <c r="E62">
-        <v>-7.368376868160206</v>
+        <v>-12.47723381240914</v>
       </c>
       <c r="F62">
-        <v>0.6632471244171668</v>
+        <v>-0.08924430938811249</v>
       </c>
       <c r="G62">
-        <v>-5.314401121938324</v>
+        <v>-8.063301095324142</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-1.142210869394781</v>
       </c>
       <c r="E63">
-        <v>-6.756903718017024</v>
+        <v>-11.81909933303151</v>
       </c>
       <c r="F63">
-        <v>0.6138946512931779</v>
+        <v>0.277203892057916</v>
       </c>
       <c r="G63">
-        <v>-5.541898794863345</v>
+        <v>-7.878371612957224</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-1.778900539117431</v>
       </c>
       <c r="E64">
-        <v>-6.624100632694307</v>
+        <v>-12.0077008125033</v>
       </c>
       <c r="F64">
-        <v>0.3815972372609181</v>
+        <v>-0.07663490078269841</v>
       </c>
       <c r="G64">
-        <v>-6.654501542045956</v>
+        <v>-7.6844246187726</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-2.386492503558289</v>
       </c>
       <c r="E65">
-        <v>-5.457430345859371</v>
+        <v>-11.08643547642984</v>
       </c>
       <c r="F65">
-        <v>0.5458774038493105</v>
+        <v>0.1504040369765901</v>
       </c>
       <c r="G65">
-        <v>-6.182653839860278</v>
+        <v>-7.991093121423131</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-2.955167544675042</v>
       </c>
       <c r="E66">
-        <v>-6.345411846375662</v>
+        <v>-12.32651377343112</v>
       </c>
       <c r="F66">
-        <v>0.1317516881677536</v>
+        <v>-0.07431464368745699</v>
       </c>
       <c r="G66">
-        <v>-6.784607998744087</v>
+        <v>-7.916216966550002</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-3.468589756083942</v>
       </c>
       <c r="E67">
-        <v>-6.895791257930616</v>
+        <v>-11.51372201073952</v>
       </c>
       <c r="F67">
-        <v>0.5130980773531312</v>
+        <v>-0.1411208179884315</v>
       </c>
       <c r="G67">
-        <v>-6.470352672311781</v>
+        <v>-8.044592499584224</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-3.916250815497846</v>
       </c>
       <c r="E68">
-        <v>-6.249979356553752</v>
+        <v>-11.46986409914933</v>
       </c>
       <c r="F68">
-        <v>0.1416034616892481</v>
+        <v>-0.2796097654906613</v>
       </c>
       <c r="G68">
-        <v>-6.018064668602723</v>
+        <v>-8.46847560214197</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-4.29165943143836</v>
       </c>
       <c r="E69">
-        <v>-5.192480382603259</v>
+        <v>-11.67250758611037</v>
       </c>
       <c r="F69">
-        <v>-0.05247970731706483</v>
+        <v>-0.3425516058575761</v>
       </c>
       <c r="G69">
-        <v>-7.068667453235577</v>
+        <v>-8.268352891627067</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-4.588283778169786</v>
       </c>
       <c r="E70">
-        <v>-5.885190346260086</v>
+        <v>-11.61756475349421</v>
       </c>
       <c r="F70">
-        <v>-0.3038651914120336</v>
+        <v>-0.187240173139294</v>
       </c>
       <c r="G70">
-        <v>-6.139513896236722</v>
+        <v>-8.098821580858534</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-4.810782960720823</v>
       </c>
       <c r="E71">
-        <v>-6.423554517452311</v>
+        <v>-11.32221743655168</v>
       </c>
       <c r="F71">
-        <v>-0.05744576989684787</v>
+        <v>-0.1252981722275582</v>
       </c>
       <c r="G71">
-        <v>-5.925328409981788</v>
+        <v>-8.209304375837561</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-4.963838964993774</v>
       </c>
       <c r="E72">
-        <v>-6.89713689839986</v>
+        <v>-10.75004197196402</v>
       </c>
       <c r="F72">
-        <v>-0.3913333338410362</v>
+        <v>-0.3298635023488961</v>
       </c>
       <c r="G72">
-        <v>-6.26907470731531</v>
+        <v>-8.457872062985162</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-5.056141704153166</v>
       </c>
       <c r="E73">
-        <v>-7.409501966698658</v>
+        <v>-11.17670137136366</v>
       </c>
       <c r="F73">
-        <v>0.1762433013721151</v>
+        <v>-0.2663500884740496</v>
       </c>
       <c r="G73">
-        <v>-5.39656386496525</v>
+        <v>-8.179235125009415</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-5.099154228631295</v>
       </c>
       <c r="E74">
-        <v>-6.912424869286554</v>
+        <v>-11.62403960994962</v>
       </c>
       <c r="F74">
-        <v>-0.5975843916270711</v>
+        <v>-0.3919024222467595</v>
       </c>
       <c r="G74">
-        <v>-6.131927072454947</v>
+        <v>-8.72800711119995</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-5.10122502728299</v>
       </c>
       <c r="E75">
-        <v>-7.634460658107995</v>
+        <v>-11.41590557761716</v>
       </c>
       <c r="F75">
-        <v>-0.2339526393505609</v>
+        <v>-0.491538453455484</v>
       </c>
       <c r="G75">
-        <v>-4.995331582480005</v>
+        <v>-8.370042698823225</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-5.070373207321046</v>
       </c>
       <c r="E76">
-        <v>-9.266058033489537</v>
+        <v>-12.62113427839181</v>
       </c>
       <c r="F76">
-        <v>-0.2084778566122677</v>
+        <v>-0.3450797831709202</v>
       </c>
       <c r="G76">
-        <v>-5.344803242701838</v>
+        <v>-8.390607533967424</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-5.007136134107296</v>
       </c>
       <c r="E77">
-        <v>-7.220397948656565</v>
+        <v>-12.72950402149056</v>
       </c>
       <c r="F77">
-        <v>0.02178260197650805</v>
+        <v>-0.2832073651210195</v>
       </c>
       <c r="G77">
-        <v>-5.414758144020719</v>
+        <v>-8.003674299607706</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-4.90976749625066</v>
       </c>
       <c r="E78">
-        <v>-9.366474376901243</v>
+        <v>-13.08272218503325</v>
       </c>
       <c r="F78">
-        <v>-0.2560766759445301</v>
+        <v>-0.5690007460260713</v>
       </c>
       <c r="G78">
-        <v>-5.477606598562589</v>
+        <v>-7.730287569004687</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-4.772165771548066</v>
       </c>
       <c r="E79">
-        <v>-7.913411096740105</v>
+        <v>-13.66667200372679</v>
       </c>
       <c r="F79">
-        <v>-0.5367938214052266</v>
+        <v>-0.4561298888228191</v>
       </c>
       <c r="G79">
-        <v>-4.685694663229378</v>
+        <v>-7.547590273263171</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-4.584434942512719</v>
       </c>
       <c r="E80">
-        <v>-10.97196881910624</v>
+        <v>-14.43171844902816</v>
       </c>
       <c r="F80">
-        <v>-0.211286022107758</v>
+        <v>-0.1662650821330077</v>
       </c>
       <c r="G80">
-        <v>-4.244567592647331</v>
+        <v>-7.520963289178407</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-4.338687202170316</v>
       </c>
       <c r="E81">
-        <v>-11.01607592337592</v>
+        <v>-15.86485877446409</v>
       </c>
       <c r="F81">
-        <v>-0.4711183686090734</v>
+        <v>-0.6490144101972812</v>
       </c>
       <c r="G81">
-        <v>-3.938919891131925</v>
+        <v>-7.405544881549879</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-4.024102485157825</v>
       </c>
       <c r="E82">
-        <v>-11.54335102033085</v>
+        <v>-15.75175437045504</v>
       </c>
       <c r="F82">
-        <v>-0.1841984080362142</v>
+        <v>-0.61813121668611</v>
       </c>
       <c r="G82">
-        <v>-3.841366808740386</v>
+        <v>-7.611885080308518</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-3.639317595114538</v>
       </c>
       <c r="E83">
-        <v>-12.65886205006655</v>
+        <v>-16.49578556645277</v>
       </c>
       <c r="F83">
-        <v>-0.1218355964838562</v>
+        <v>-0.2447197588521489</v>
       </c>
       <c r="G83">
-        <v>-3.98458964626427</v>
+        <v>-6.774441759306291</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-3.186078076766782</v>
       </c>
       <c r="E84">
-        <v>-13.05656526010948</v>
+        <v>-17.82913668338705</v>
       </c>
       <c r="F84">
-        <v>-0.4169406553637773</v>
+        <v>-0.3956839194405392</v>
       </c>
       <c r="G84">
-        <v>-3.54491153893029</v>
+        <v>-6.426745405406415</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-2.668630488008875</v>
       </c>
       <c r="E85">
-        <v>-14.66036934530527</v>
+        <v>-18.22475498134492</v>
       </c>
       <c r="F85">
-        <v>-0.3388512886692707</v>
+        <v>-0.2916641679361997</v>
       </c>
       <c r="G85">
-        <v>-4.284692126268151</v>
+        <v>-6.756537272900436</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-2.101274787821255</v>
       </c>
       <c r="E86">
-        <v>-14.86235662487698</v>
+        <v>-18.83528950572869</v>
       </c>
       <c r="F86">
-        <v>-0.3741190308434597</v>
+        <v>0.2056296349864275</v>
       </c>
       <c r="G86">
-        <v>-3.312307249585052</v>
+        <v>-6.125397600232573</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-1.495525650151132</v>
       </c>
       <c r="E87">
-        <v>-16.95515565824676</v>
+        <v>-20.3139407208621</v>
       </c>
       <c r="F87">
-        <v>-0.4398060807832521</v>
+        <v>-0.0575658831702538</v>
       </c>
       <c r="G87">
-        <v>-3.206128267064475</v>
+        <v>-6.050907835558928</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-0.8691353553533906</v>
       </c>
       <c r="E88">
-        <v>-18.06266760297083</v>
+        <v>-21.41069169504354</v>
       </c>
       <c r="F88">
-        <v>-0.3767060222424025</v>
+        <v>-0.2037230277201986</v>
       </c>
       <c r="G88">
-        <v>-3.150501132061624</v>
+        <v>-5.929565648453165</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-0.2436330976197509</v>
       </c>
       <c r="E89">
-        <v>-19.62819984580833</v>
+        <v>-22.19648343091243</v>
       </c>
       <c r="F89">
-        <v>-0.5673348991790416</v>
+        <v>-0.118853473833778</v>
       </c>
       <c r="G89">
-        <v>-3.610879833258541</v>
+        <v>-5.814805148461598</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>0.3628966007574749</v>
       </c>
       <c r="E90">
-        <v>-21.26198596355806</v>
+        <v>-24.28967701935806</v>
       </c>
       <c r="F90">
-        <v>-0.2003880205565278</v>
+        <v>0.05740074356208119</v>
       </c>
       <c r="G90">
-        <v>-2.657488123475791</v>
+        <v>-5.574684525438546</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>0.926133107335386</v>
       </c>
       <c r="E91">
-        <v>-23.765072437285</v>
+        <v>-25.65135303752767</v>
       </c>
       <c r="F91">
-        <v>-0.4374005018455223</v>
+        <v>-0.1918955979430272</v>
       </c>
       <c r="G91">
-        <v>-2.713747058669691</v>
+        <v>-5.179778077097567</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>1.426314938728802</v>
       </c>
       <c r="E92">
-        <v>-24.09890756357471</v>
+        <v>-27.97469267832736</v>
       </c>
       <c r="F92">
-        <v>-0.4395691677060514</v>
+        <v>-0.2651920308449359</v>
       </c>
       <c r="G92">
-        <v>-2.511777246356576</v>
+        <v>-5.629298691540044</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>1.846703559165193</v>
       </c>
       <c r="E93">
-        <v>-26.4227331300994</v>
+        <v>-29.28739610516025</v>
       </c>
       <c r="F93">
-        <v>-0.6750806472611732</v>
+        <v>0.06791355427100972</v>
       </c>
       <c r="G93">
-        <v>-2.859202082818977</v>
+        <v>-5.510423658072883</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>2.170027152670774</v>
       </c>
       <c r="E94">
-        <v>-29.20558822508944</v>
+        <v>-32.00654716824441</v>
       </c>
       <c r="F94">
-        <v>-0.8442846296918058</v>
+        <v>-0.2082981008858602</v>
       </c>
       <c r="G94">
-        <v>-2.275810317977984</v>
+        <v>-5.154143175957426</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>2.388704980987312</v>
       </c>
       <c r="E95">
-        <v>-30.78981822531131</v>
+        <v>-33.93809777192772</v>
       </c>
       <c r="F95">
-        <v>-1.442213474910934</v>
+        <v>-0.275313852139743</v>
       </c>
       <c r="G95">
-        <v>-2.768590970295208</v>
+        <v>-5.474883591954057</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>2.492280625175029</v>
       </c>
       <c r="E96">
-        <v>-33.07838095108255</v>
+        <v>-35.64235973264847</v>
       </c>
       <c r="F96">
-        <v>-1.363106873045789</v>
+        <v>-0.6702777730597417</v>
       </c>
       <c r="G96">
-        <v>-3.384697975607441</v>
+        <v>-5.034390932307651</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>2.48448849327056</v>
       </c>
       <c r="E97">
-        <v>-34.72160108835662</v>
+        <v>-37.46836893014523</v>
       </c>
       <c r="F97">
-        <v>-1.126789392007744</v>
+        <v>-0.6556993351378733</v>
       </c>
       <c r="G97">
-        <v>-3.256808041067166</v>
+        <v>-5.066701507367269</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>2.360423668607118</v>
       </c>
       <c r="E98">
-        <v>-37.6283132514757</v>
+        <v>-39.40339992491874</v>
       </c>
       <c r="F98">
-        <v>-1.550159687904543</v>
+        <v>-0.548802663643611</v>
       </c>
       <c r="G98">
-        <v>-3.907188901371534</v>
+        <v>-5.321340481061504</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>2.146426347235064</v>
       </c>
       <c r="E99">
-        <v>-41.14733336021425</v>
+        <v>-42.01988983387012</v>
       </c>
       <c r="F99">
-        <v>-1.015624971654258</v>
+        <v>-0.5906840911617512</v>
       </c>
       <c r="G99">
-        <v>-3.829829928392257</v>
+        <v>-5.506290849385151</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>1.834896593647602</v>
       </c>
       <c r="E100">
-        <v>-43.38123359513375</v>
+        <v>-44.70832997581284</v>
       </c>
       <c r="F100">
-        <v>-1.528753017481398</v>
+        <v>-0.960486352221715</v>
       </c>
       <c r="G100">
-        <v>-3.672793641236793</v>
+        <v>-5.334725768580141</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>1.492531102199407</v>
       </c>
       <c r="E101">
-        <v>-44.71460547812465</v>
+        <v>-46.40552005595023</v>
       </c>
       <c r="F101">
-        <v>-1.653545738345741</v>
+        <v>-1.054738823679646</v>
       </c>
       <c r="G101">
-        <v>-3.841262378956741</v>
+        <v>-5.190265438120069</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>1.077055406413836</v>
       </c>
       <c r="E102">
-        <v>-47.65826876240073</v>
+        <v>-48.52367548276091</v>
       </c>
       <c r="F102">
-        <v>-1.923136252852034</v>
+        <v>-1.145196544065352</v>
       </c>
       <c r="G102">
-        <v>-4.394359063562455</v>
+        <v>-5.642931999794838</v>
       </c>
     </row>
   </sheetData>
